--- a/data/trans_dic/IP1003-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen Alergias crónicas</t>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,26</t>
+          <t>4,8; 13,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 11,78</t>
+          <t>4,27; 12,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 8,09</t>
+          <t>1,4; 7,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,37</t>
+          <t>4,66; 13,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 13,5</t>
+          <t>5,64; 13,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,7</t>
+          <t>2,36; 7,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,89</t>
+          <t>3,21; 10,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 15,89</t>
+          <t>4,77; 15,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,61</t>
+          <t>6,16; 11,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,74</t>
+          <t>3,85; 8,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,67</t>
+          <t>2,93; 7,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 12,8</t>
+          <t>5,92; 12,56</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 8,87</t>
+          <t>3,56; 8,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,86</t>
+          <t>1,64; 5,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,65</t>
+          <t>3,52; 8,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,65</t>
+          <t>4,69; 11,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,99</t>
+          <t>4,75; 10,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,3</t>
+          <t>5,34; 11,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,15</t>
+          <t>4,53; 10,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 13,45</t>
+          <t>6,24; 13,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,67</t>
+          <t>4,9; 8,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,85</t>
+          <t>4,0; 7,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,45</t>
+          <t>4,64; 8,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,23</t>
+          <t>6,67; 11,27</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,0</t>
+          <t>2,48; 8,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,95</t>
+          <t>2,33; 8,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,88</t>
+          <t>1,68; 6,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,21</t>
+          <t>1,27; 6,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,96</t>
+          <t>3,39; 9,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,33</t>
+          <t>3,0; 8,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,02</t>
+          <t>1,43; 6,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 10,11</t>
+          <t>3,02; 10,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,85</t>
+          <t>3,43; 7,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,2</t>
+          <t>3,18; 6,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,55</t>
+          <t>2,27; 5,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,22</t>
+          <t>2,72; 7,12</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 8,35</t>
+          <t>3,15; 8,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,78</t>
+          <t>2,55; 7,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,78</t>
+          <t>2,95; 8,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,9</t>
+          <t>1,78; 7,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,08</t>
+          <t>3,51; 8,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,0</t>
+          <t>3,49; 9,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,95</t>
+          <t>2,04; 6,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 13,34</t>
+          <t>4,93; 13,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,84</t>
+          <t>3,82; 7,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,25</t>
+          <t>3,53; 7,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,47</t>
+          <t>2,97; 6,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,89</t>
+          <t>4,29; 9,26</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,46</t>
+          <t>4,71; 7,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,18</t>
+          <t>3,43; 6,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,08</t>
+          <t>3,39; 6,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,18</t>
+          <t>4,0; 7,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,44</t>
+          <t>5,56; 8,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,7</t>
+          <t>4,64; 7,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,7</t>
+          <t>3,92; 6,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,45</t>
+          <t>6,47; 10,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,61</t>
+          <t>5,47; 7,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,52</t>
+          <t>4,53; 6,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,92</t>
+          <t>4,04; 5,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,2</t>
+          <t>5,81; 8,36</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11877</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9936</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4724</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7007</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8723</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12650</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>25378</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16943</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13447</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>22112</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6654; 18160</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5826; 16512</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1868; 10361</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5461; 15247</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8636; 20482</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3615; 11858</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4750; 15265</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6646; 21333</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>17973; 33684</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11152; 26007</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8254; 21398</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>15184; 32236</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10974</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6664</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11592</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14615</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17999</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15717</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>23932</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>26873</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>24664</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27309</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>38547</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6940; 16362</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3370; 11460</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7305; 17759</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8930; 22624</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10086; 23141</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11860; 25344</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10153; 22657</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>15912; 34457</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>19940; 35671</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>17080; 33022</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>20009; 36238</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>29728; 50202</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6437</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7072</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5723</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5959</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8963</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8462</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5890</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10836</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15400</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15534</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11613</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>16795</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3419; 11079</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3600; 13081</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2624; 10271</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2399; 11430</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5078; 14586</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4983; 14040</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2386; 11086</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5566; 19055</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9850; 22550</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10173; 22212</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7319; 17730</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>10159; 26565</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>11351</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9517</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10092</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6566</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11604</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12200</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8270</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15217</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>22954</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>21717</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18362</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>21783</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6586; 18003</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5373; 16151</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6110; 17693</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2974; 12130</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>7291; 18390</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7227; 19601</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4188; 13339</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8937; 23804</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>15933; 31609</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>14738; 31283</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>12287; 26282</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>14940; 32294</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>40639</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33189</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>32132</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>36603</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>62635</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>90606</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>78857</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99238</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>32109; 51320</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24255; 43089</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23846; 43540</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26562; 47281</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>40194; 61202</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>34688; 57298</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>29223; 50166</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>49192; 80052</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>76829; 107294</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>65827; 94505</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>58482; 86083</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>82784; 119073</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1003-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 13,09</t>
+          <t>5,15; 13,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 12,11</t>
+          <t>3,91; 11,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,75</t>
+          <t>1,53; 7,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 13,0</t>
+          <t>5,01; 12,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 13,38</t>
+          <t>5,6; 13,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,75</t>
+          <t>2,3; 8,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 10,31</t>
+          <t>2,73; 9,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 15,3</t>
+          <t>4,8; 15,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,54</t>
+          <t>6,41; 11,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,98</t>
+          <t>3,88; 8,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,59</t>
+          <t>2,94; 7,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,56</t>
+          <t>5,97; 12,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,38</t>
+          <t>3,41; 8,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,58</t>
+          <t>1,64; 5,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,57</t>
+          <t>3,41; 8,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,88</t>
+          <t>4,74; 11,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 10,91</t>
+          <t>4,76; 10,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 11,42</t>
+          <t>5,16; 11,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,1</t>
+          <t>4,57; 10,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,51</t>
+          <t>6,23; 14,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,76</t>
+          <t>4,88; 8,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,73</t>
+          <t>4,06; 8,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,4</t>
+          <t>4,68; 8,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 11,27</t>
+          <t>6,13; 11,21</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,04</t>
+          <t>2,53; 8,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,48</t>
+          <t>2,37; 7,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,58</t>
+          <t>1,7; 6,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,06</t>
+          <t>1,46; 6,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,75</t>
+          <t>3,46; 9,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 8,46</t>
+          <t>2,92; 8,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,65</t>
+          <t>1,5; 6,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,33</t>
+          <t>2,82; 9,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,84</t>
+          <t>3,65; 7,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,94</t>
+          <t>3,29; 6,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,49</t>
+          <t>2,18; 5,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,12</t>
+          <t>2,65; 6,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,6</t>
+          <t>3,12; 8,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,68</t>
+          <t>2,45; 7,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,53</t>
+          <t>2,8; 8,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,25</t>
+          <t>1,89; 7,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,85</t>
+          <t>3,52; 9,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,47</t>
+          <t>3,52; 9,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,48</t>
+          <t>1,97; 6,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,13</t>
+          <t>4,92; 12,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,58</t>
+          <t>3,76; 7,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,5</t>
+          <t>3,46; 7,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,36</t>
+          <t>2,91; 6,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 9,26</t>
+          <t>4,18; 9,21</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,54</t>
+          <t>4,53; 7,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,1</t>
+          <t>3,53; 6,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,18</t>
+          <t>3,35; 5,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,12</t>
+          <t>4,13; 7,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,47</t>
+          <t>5,42; 8,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,66</t>
+          <t>4,68; 7,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,74</t>
+          <t>3,98; 6,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,53</t>
+          <t>6,48; 10,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 7,64</t>
+          <t>5,52; 7,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,5</t>
+          <t>4,51; 6,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,94</t>
+          <t>3,97; 5,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,36</t>
+          <t>5,56; 8,33</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6654; 18160</t>
+          <t>7140; 18307</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5826; 16512</t>
+          <t>5335; 16002</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1868; 10361</t>
+          <t>2039; 10084</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5461; 15247</t>
+          <t>5876; 15211</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8636; 20482</t>
+          <t>8572; 20341</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3615; 11858</t>
+          <t>3517; 12438</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4750; 15265</t>
+          <t>4049; 14715</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6646; 21333</t>
+          <t>6690; 21767</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17973; 33684</t>
+          <t>18697; 34566</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11152; 26007</t>
+          <t>11223; 24300</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8254; 21398</t>
+          <t>8297; 21336</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15184; 32236</t>
+          <t>15319; 32077</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6940; 16362</t>
+          <t>6660; 16333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3370; 11460</t>
+          <t>3375; 11622</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7305; 17759</t>
+          <t>7057; 17324</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8930; 22624</t>
+          <t>9029; 21268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10086; 23141</t>
+          <t>10089; 22788</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11860; 25344</t>
+          <t>11446; 24828</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10153; 22657</t>
+          <t>10255; 23366</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15912; 34457</t>
+          <t>15888; 35763</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19940; 35671</t>
+          <t>19883; 35286</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17080; 33022</t>
+          <t>17331; 34306</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20009; 36238</t>
+          <t>20202; 36581</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29728; 50202</t>
+          <t>27320; 49925</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3419; 11079</t>
+          <t>3493; 11396</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3600; 13081</t>
+          <t>3651; 12270</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2624; 10271</t>
+          <t>2658; 10852</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2399; 11430</t>
+          <t>2751; 12258</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5078; 14586</t>
+          <t>5182; 14474</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4983; 14040</t>
+          <t>4847; 13801</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2386; 11086</t>
+          <t>2504; 10864</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5566; 19055</t>
+          <t>5208; 18009</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9850; 22550</t>
+          <t>10495; 22348</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10173; 22212</t>
+          <t>10525; 22391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7319; 17730</t>
+          <t>7045; 18355</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10159; 26565</t>
+          <t>9907; 25158</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6586; 18003</t>
+          <t>6532; 18072</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5373; 16151</t>
+          <t>5158; 15713</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6110; 17693</t>
+          <t>5811; 17095</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2974; 12130</t>
+          <t>3162; 12355</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7291; 18390</t>
+          <t>7308; 18932</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7227; 19601</t>
+          <t>7281; 18920</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4188; 13339</t>
+          <t>4059; 13805</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8937; 23804</t>
+          <t>8910; 23503</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15933; 31609</t>
+          <t>15673; 30809</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14738; 31283</t>
+          <t>14430; 30230</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12287; 26282</t>
+          <t>12015; 26328</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14940; 32294</t>
+          <t>14556; 32098</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32109; 51320</t>
+          <t>30846; 51436</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24255; 43089</t>
+          <t>24901; 44335</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23846; 43540</t>
+          <t>23611; 41695</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26562; 47281</t>
+          <t>27416; 50068</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40194; 61202</t>
+          <t>39158; 60760</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34688; 57298</t>
+          <t>35045; 56959</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29223; 50166</t>
+          <t>29652; 50237</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49192; 80052</t>
+          <t>49293; 79927</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>76829; 107294</t>
+          <t>77445; 107716</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65827; 94505</t>
+          <t>65552; 95580</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58482; 86083</t>
+          <t>57546; 85532</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82784; 119073</t>
+          <t>79215; 118587</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1003-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,56%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,28%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,53%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 13,2</t>
+          <t>5,79; 13,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 11,73</t>
+          <t>2,24; 7,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,54</t>
+          <t>3,16; 9,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 12,97</t>
+          <t>4,96; 16,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 13,29</t>
+          <t>5,17; 13,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 8,12</t>
+          <t>3,99; 11,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,94</t>
+          <t>1,32; 8,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 15,61</t>
+          <t>4,87; 12,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 11,85</t>
+          <t>6,47; 11,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,39</t>
+          <t>3,78; 8,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,57</t>
+          <t>2,88; 7,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 12,5</t>
+          <t>5,99; 13,03</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,62%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,59%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,37</t>
+          <t>5,0; 10,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,66</t>
+          <t>5,24; 11,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,36</t>
+          <t>4,37; 10,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 11,16</t>
+          <t>6,38; 13,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 10,74</t>
+          <t>3,55; 8,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 11,18</t>
+          <t>1,64; 5,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 10,41</t>
+          <t>3,34; 8,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 14,02</t>
+          <t>5,25; 12,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,66</t>
+          <t>4,86; 8,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,03</t>
+          <t>4,07; 7,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,48</t>
+          <t>4,5; 8,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,21</t>
+          <t>6,39; 11,23</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,67%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,59%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,27</t>
+          <t>3,62; 9,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,96</t>
+          <t>2,78; 8,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,96</t>
+          <t>1,49; 7,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,49</t>
+          <t>3,38; 11,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,67</t>
+          <t>2,35; 8,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,31</t>
+          <t>2,32; 7,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,52</t>
+          <t>1,77; 6,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,76</t>
+          <t>1,88; 7,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,77</t>
+          <t>3,57; 7,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,99</t>
+          <t>3,25; 7,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,69</t>
+          <t>2,17; 5,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,74</t>
+          <t>3,32; 8,28</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,53%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,87%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,63</t>
+          <t>3,54; 9,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,47</t>
+          <t>3,57; 9,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,24</t>
+          <t>2,08; 6,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,38</t>
+          <t>4,84; 12,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,11</t>
+          <t>3,2; 8,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,14</t>
+          <t>2,55; 7,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,71</t>
+          <t>2,58; 7,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,97</t>
+          <t>1,86; 7,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,39</t>
+          <t>3,88; 7,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,24</t>
+          <t>3,63; 7,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,37</t>
+          <t>2,88; 6,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,21</t>
+          <t>4,15; 8,54</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>4,56%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,55</t>
+          <t>5,43; 8,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,28</t>
+          <t>4,81; 7,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,92</t>
+          <t>3,92; 6,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,54</t>
+          <t>6,49; 10,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,41</t>
+          <t>4,59; 7,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,61</t>
+          <t>3,45; 6,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,74</t>
+          <t>3,29; 6,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,51</t>
+          <t>4,66; 8,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 7,67</t>
+          <t>5,46; 7,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,57</t>
+          <t>4,48; 6,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 5,9</t>
+          <t>4,01; 5,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,33</t>
+          <t>6,01; 8,58</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7007</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8723</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11890</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>11877</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9936</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4724</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9462</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13502</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7007</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8723</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22118</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7140; 18307</t>
+          <t>8866; 20667</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5335; 16002</t>
+          <t>3426; 11791</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2039; 10084</t>
+          <t>4680; 14652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5876; 15211</t>
+          <t>6194; 21172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8572; 20341</t>
+          <t>7168; 18394</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3517; 12438</t>
+          <t>5438; 16070</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4049; 14715</t>
+          <t>1769; 10811</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6690; 21767</t>
+          <t>5900; 15578</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18697; 34566</t>
+          <t>18881; 33887</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11223; 24300</t>
+          <t>10941; 25303</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8297; 21336</t>
+          <t>8128; 21626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15319; 32077</t>
+          <t>14734; 32056</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17999</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15717</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21950</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10974</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6664</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11592</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14615</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15899</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17999</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15717</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23932</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>36803</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6660; 16333</t>
+          <t>10615; 23314</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3375; 11622</t>
+          <t>11634; 25089</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7057; 17324</t>
+          <t>9809; 22772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9029; 21268</t>
+          <t>15138; 31624</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10089; 22788</t>
+          <t>6937; 17305</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11446; 24828</t>
+          <t>3364; 12045</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10255; 23366</t>
+          <t>6913; 17935</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15888; 35763</t>
+          <t>9684; 22431</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19883; 35286</t>
+          <t>19783; 35296</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17331; 34306</t>
+          <t>17392; 33538</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20202; 36581</t>
+          <t>19416; 36492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27320; 49925</t>
+          <t>26950; 47328</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8963</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8462</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5890</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10896</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6437</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7072</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5723</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5959</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8963</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8462</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5890</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16795</t>
+          <t>17156</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3493; 11396</t>
+          <t>5415; 14908</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3651; 12270</t>
+          <t>4621; 13823</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2658; 10852</t>
+          <t>2477; 11697</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2751; 12258</t>
+          <t>5664; 18703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5182; 14474</t>
+          <t>3232; 11026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4847; 13801</t>
+          <t>3573; 12257</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2504; 10864</t>
+          <t>2765; 10738</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5208; 18009</t>
+          <t>2918; 12236</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10495; 22348</t>
+          <t>10265; 22564</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10525; 22391</t>
+          <t>10416; 23059</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7045; 18355</t>
+          <t>7000; 17903</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9907; 25158</t>
+          <t>10721; 26752</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11604</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12200</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8270</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13742</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>11351</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9517</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>10092</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6566</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11604</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12200</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8270</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>20523</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6532; 18072</t>
+          <t>7361; 18862</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5158; 15713</t>
+          <t>7386; 18638</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5811; 17095</t>
+          <t>4274; 14301</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3162; 12355</t>
+          <t>8198; 21186</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7308; 18932</t>
+          <t>6690; 17473</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7281; 18920</t>
+          <t>5370; 16351</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4059; 13805</t>
+          <t>5344; 16146</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8910; 23503</t>
+          <t>3092; 12247</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15673; 30809</t>
+          <t>16204; 32707</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14430; 30230</t>
+          <t>15167; 30241</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12015; 26328</t>
+          <t>11919; 26742</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14556; 32098</t>
+          <t>13953; 28699</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>58479</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>40639</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>33189</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>32132</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>36603</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>49967</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38600</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>96599</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30846; 51436</t>
+          <t>39235; 60973</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24901; 44335</t>
+          <t>35965; 57637</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23611; 41695</t>
+          <t>29165; 49869</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27416; 50068</t>
+          <t>45376; 72397</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>39158; 60760</t>
+          <t>31291; 50830</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35045; 56959</t>
+          <t>24394; 43668</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29652; 50237</t>
+          <t>23158; 42850</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49293; 79927</t>
+          <t>29234; 50580</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77445; 107716</t>
+          <t>76611; 106770</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65552; 95580</t>
+          <t>65194; 94771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57546; 85532</t>
+          <t>58078; 85840</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>79215; 118587</t>
+          <t>79789; 113760</t>
         </is>
       </c>
     </row>
